--- a/materials/05_행정처리_도움받기/2022 오현초 교구 견적서(마샬 액톤 외).xlsx
+++ b/materials/05_행정처리_도움받기/2022 오현초 교구 견적서(마샬 액톤 외).xlsx
@@ -1488,7 +1488,7 @@
       <c r="G5" s="70" t="n"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>성명 | 홍 길 동 (인)</t>
+          <t>성명 | 탁 현 수 (인)</t>
         </is>
       </c>
     </row>
